--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444969144207771</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>35697386</v>
+        <v>4058799</v>
       </c>
       <c r="L2" t="n">
-        <v>19969192</v>
+        <v>1954563</v>
       </c>
       <c r="M2" t="n">
-        <v>4834480</v>
+        <v>418447</v>
       </c>
       <c r="N2" t="n">
-        <v>198927</v>
+        <v>10074</v>
       </c>
       <c r="O2" t="n">
-        <v>2847671</v>
+        <v>233370</v>
       </c>
       <c r="P2" t="n">
-        <v>1130823</v>
+        <v>94207</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999001622200012</v>
+        <v>0.999871551990509</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8730517029762268</v>
+        <v>0.7787453532218933</v>
       </c>
       <c r="S2" t="n">
-        <v>0.75592041015625</v>
+        <v>0.5975239276885986</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6927378177642822</v>
+        <v>0.4889501929283142</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2972880005836487</v>
+        <v>0.08546849340200424</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7474867105484009</v>
+        <v>0.5534593462944031</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8283088803291321</v>
+        <v>0.6856254935264587</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024809124862332</v>
       </c>
       <c r="C3" t="n">
-        <v>3009</v>
+        <v>553</v>
       </c>
       <c r="D3" t="n">
-        <v>35697386</v>
+        <v>4058799</v>
       </c>
       <c r="E3" t="n">
-        <v>4325876</v>
+        <v>892708</v>
       </c>
       <c r="F3" t="n">
-        <v>99463</v>
+        <v>32356</v>
       </c>
       <c r="G3" t="n">
-        <v>8158</v>
+        <v>2207</v>
       </c>
       <c r="H3" t="n">
-        <v>5780</v>
+        <v>1938</v>
       </c>
       <c r="I3" t="n">
-        <v>301</v>
+        <v>123</v>
       </c>
       <c r="J3" t="n">
-        <v>80127932</v>
+        <v>10015811</v>
       </c>
       <c r="K3" t="n">
-        <v>85306158</v>
+        <v>10187743</v>
       </c>
       <c r="L3" t="n">
-        <v>98005072</v>
+        <v>11717148</v>
       </c>
       <c r="M3" t="n">
-        <v>121021660</v>
+        <v>14954300</v>
       </c>
       <c r="N3" t="n">
-        <v>129452529</v>
+        <v>16132202</v>
       </c>
       <c r="O3" t="n">
-        <v>125597670</v>
+        <v>15630420</v>
       </c>
       <c r="P3" t="n">
-        <v>128855282</v>
+        <v>16092814</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8893226385116577</v>
+        <v>0.8136011362075806</v>
       </c>
       <c r="S3" t="n">
-        <v>0.762652575969696</v>
+        <v>0.5930266380310059</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6471152305603027</v>
+        <v>0.446134090423584</v>
       </c>
       <c r="U3" t="n">
-        <v>0.278586208820343</v>
+        <v>0.1124280169606209</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6984481811523438</v>
+        <v>0.4567884206771851</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7309203743934631</v>
+        <v>0.4866315424442291</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319507024117701</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4857663</v>
+        <v>1067479</v>
       </c>
       <c r="E4" t="n">
-        <v>19969192</v>
+        <v>1954563</v>
       </c>
       <c r="F4" t="n">
-        <v>1193554</v>
+        <v>229227</v>
       </c>
       <c r="G4" t="n">
-        <v>52354</v>
+        <v>14959</v>
       </c>
       <c r="H4" t="n">
-        <v>102060</v>
+        <v>26832</v>
       </c>
       <c r="I4" t="n">
-        <v>9030</v>
+        <v>2851</v>
       </c>
       <c r="J4" t="n">
-        <v>5044</v>
+        <v>811</v>
       </c>
       <c r="K4" t="n">
-        <v>5190669</v>
+        <v>1153173</v>
       </c>
       <c r="L4" t="n">
-        <v>6447864</v>
+        <v>1316541</v>
       </c>
       <c r="M4" t="n">
-        <v>2144322</v>
+        <v>437360</v>
       </c>
       <c r="N4" t="n">
-        <v>470212</v>
+        <v>107794</v>
       </c>
       <c r="O4" t="n">
-        <v>961990</v>
+        <v>188287</v>
       </c>
       <c r="P4" t="n">
-        <v>234396</v>
+        <v>43196</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999950110912323</v>
+        <v>0.9999358057975769</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8811120390892029</v>
+        <v>0.7957917451858521</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7592715620994568</v>
+        <v>0.5952668190002441</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6691498160362244</v>
+        <v>0.4665619134902954</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2876334190368652</v>
+        <v>0.09711189568042755</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7221358418464661</v>
+        <v>0.5004986524581909</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7765732407569885</v>
+        <v>0.5692386031150818</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1388</v>
+        <v>174</v>
       </c>
       <c r="D5" t="n">
-        <v>225496</v>
+        <v>62255</v>
       </c>
       <c r="E5" t="n">
-        <v>1778839</v>
+        <v>338961</v>
       </c>
       <c r="F5" t="n">
-        <v>4834480</v>
+        <v>418447</v>
       </c>
       <c r="G5" t="n">
-        <v>158962</v>
+        <v>31886</v>
       </c>
       <c r="H5" t="n">
-        <v>430141</v>
+        <v>75733</v>
       </c>
       <c r="I5" t="n">
-        <v>41512</v>
+        <v>10484</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4442587</v>
+        <v>929885</v>
       </c>
       <c r="L5" t="n">
-        <v>6214672</v>
+        <v>1341348</v>
       </c>
       <c r="M5" t="n">
-        <v>2636338</v>
+        <v>519493</v>
       </c>
       <c r="N5" t="n">
-        <v>515132</v>
+        <v>79530</v>
       </c>
       <c r="O5" t="n">
-        <v>1229469</v>
+        <v>277523</v>
       </c>
       <c r="P5" t="n">
-        <v>416299</v>
+        <v>99383</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999613761901855</v>
+        <v>0.9999503493309021</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9262592196464539</v>
+        <v>0.8724367022514343</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9030706882476807</v>
+        <v>0.8372349143028259</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9634049534797668</v>
+        <v>0.9414037466049194</v>
       </c>
       <c r="U5" t="n">
-        <v>0.992457389831543</v>
+        <v>0.9885285496711731</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9832248091697693</v>
+        <v>0.9714745283126831</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9950190782546997</v>
+        <v>0.9912686944007874</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>285</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>96906</v>
+        <v>18046</v>
       </c>
       <c r="E6" t="n">
-        <v>153519</v>
+        <v>23213</v>
       </c>
       <c r="F6" t="n">
-        <v>177246</v>
+        <v>27644</v>
       </c>
       <c r="G6" t="n">
-        <v>198927</v>
+        <v>10074</v>
       </c>
       <c r="H6" t="n">
-        <v>80093</v>
+        <v>9318</v>
       </c>
       <c r="I6" t="n">
-        <v>7083</v>
+        <v>1274</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>10195</v>
+        <v>5275</v>
       </c>
       <c r="E7" t="n">
-        <v>176200</v>
+        <v>56322</v>
       </c>
       <c r="F7" t="n">
-        <v>636083</v>
+        <v>135471</v>
       </c>
       <c r="G7" t="n">
-        <v>230409</v>
+        <v>51976</v>
       </c>
       <c r="H7" t="n">
-        <v>2847671</v>
+        <v>233370</v>
       </c>
       <c r="I7" t="n">
-        <v>176470</v>
+        <v>28464</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>118</v>
       </c>
       <c r="E8" t="n">
-        <v>13430</v>
+        <v>5337</v>
       </c>
       <c r="F8" t="n">
-        <v>37976</v>
+        <v>12662</v>
       </c>
       <c r="G8" t="n">
-        <v>20329</v>
+        <v>6766</v>
       </c>
       <c r="H8" t="n">
-        <v>343916</v>
+        <v>74466</v>
       </c>
       <c r="I8" t="n">
-        <v>1130823</v>
+        <v>94207</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
